--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487208_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487208_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9985</v>
+        <v>8.536899999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8955</v>
+        <v>5.6748</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1031</v>
+        <v>2.8621</v>
       </c>
       <c r="G2" t="n">
         <v>7.6717</v>
@@ -610,13 +610,13 @@
         <v>2.7021</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1593</v>
+        <v>0.3791</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.538</v>
+        <v>0.2413</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3787</v>
+        <v>0.1378</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2859</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O. IBARROLA ITURRIA</t>
+          <t>S. JOKSIMOVIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7621</v>
+        <v>5.2805</v>
       </c>
       <c r="E3" t="n">
-        <v>3.975</v>
+        <v>3.4248</v>
       </c>
       <c r="F3" t="n">
-        <v>0.787</v>
+        <v>1.8556</v>
       </c>
       <c r="G3" t="n">
-        <v>3.079</v>
+        <v>3.8979</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2079</v>
+        <v>-0.0892</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8711</v>
+        <v>3.9871</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9124</v>
+        <v>2.8363</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2365</v>
+        <v>-0.3626</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6758</v>
+        <v>3.1988</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1667</v>
+        <v>1.0617</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0286</v>
+        <v>0.2734</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1953</v>
+        <v>0.7883</v>
       </c>
       <c r="P3" t="n">
-        <v>0.579</v>
+        <v>-0.965</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5441</v>
+        <v>1.9301</v>
       </c>
       <c r="S3" t="n">
-        <v>2.332</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3558</v>
+        <v>-0.158</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0238</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="V3" t="n">
+        <v>2.4137</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.6417</v>
+      </c>
+      <c r="X3" t="n">
         <v>-1.228</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-0.3281</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.8999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. JOKSIMOVIC</t>
+          <t>O. IBARROLA ITURRIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5547</v>
+        <v>3.3125</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6455</v>
+        <v>2.6325</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9092</v>
+        <v>0.68</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8979</v>
+        <v>3.079</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0892</v>
+        <v>0.2079</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9871</v>
+        <v>2.8711</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8363</v>
+        <v>2.9124</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3626</v>
+        <v>1.2365</v>
       </c>
       <c r="L4" t="n">
-        <v>3.1988</v>
+        <v>1.6758</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0617</v>
+        <v>0.1667</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2734</v>
+        <v>-1.0286</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7883</v>
+        <v>1.1953</v>
       </c>
       <c r="P4" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="Q4" t="n">
         <v>-0.965</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-2.8951</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.9301</v>
+        <v>1.5441</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7919</v>
+        <v>0.8824</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9373</v>
+        <v>1.0133</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1454</v>
+        <v>-0.1309</v>
       </c>
       <c r="V4" t="n">
-        <v>2.4137</v>
+        <v>-1.228</v>
       </c>
       <c r="W4" t="n">
-        <v>3.6417</v>
+        <v>-0.3281</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.228</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. ALVES DE SOUZA SILVA</t>
+          <t>A. PEREZ PEREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4274</v>
+        <v>1.4321</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8562</v>
+        <v>1.3421</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5712</v>
+        <v>0.09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7404</v>
+        <v>-0.2232</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7647</v>
+        <v>-0.3974</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0243</v>
+        <v>0.1742</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7935</v>
+        <v>-0.0097</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6714</v>
+        <v>-0.1968</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1221</v>
+        <v>0.1871</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0531</v>
+        <v>-0.2135</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09329999999999999</v>
+        <v>-0.2006</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1464</v>
+        <v>-0.0129</v>
       </c>
       <c r="P5" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-0.965</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-1.9301</v>
-      </c>
       <c r="R5" t="n">
-        <v>0.965</v>
+        <v>1.3511</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9379</v>
+        <v>0.0413</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9928</v>
+        <v>-0.1391</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0549</v>
+        <v>0.1804</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2859</v>
+        <v>1.228</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.4559</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2859</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2582</v>
+        <v>1.3911</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4865</v>
+        <v>0.6461</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.745</v>
       </c>
       <c r="G6" t="n">
         <v>0.7711</v>
@@ -922,13 +922,13 @@
         <v>0.579</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0919</v>
+        <v>0.041</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.238</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1461</v>
+        <v>0.1193</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. PEREZ PEREZ</t>
+          <t>T. ALVES DE SOUZA SILVA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.092</v>
+        <v>0.7532</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8414</v>
+        <v>0.1553</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2506</v>
+        <v>0.5979</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2232</v>
+        <v>1.7404</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3974</v>
+        <v>1.7647</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1742</v>
+        <v>-0.0243</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0097</v>
+        <v>1.7935</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1968</v>
+        <v>1.6714</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1871</v>
+        <v>0.1221</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2135</v>
+        <v>-0.0531</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2006</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0129</v>
+        <v>-0.1464</v>
       </c>
       <c r="P7" t="n">
-        <v>0.386</v>
+        <v>-0.965</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3511</v>
+        <v>0.965</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2988</v>
+        <v>0.2637</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6398</v>
+        <v>0.2918</v>
       </c>
       <c r="U7" t="n">
-        <v>0.341</v>
+        <v>-0.0281</v>
       </c>
       <c r="V7" t="n">
-        <v>1.228</v>
+        <v>-0.2859</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4559</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.228</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. DIALLO TOURE</t>
+          <t>D. PEREZ ABELLEIRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3885</v>
+        <v>-0.4344</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2656</v>
+        <v>-0.5974</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1228</v>
+        <v>0.163</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7011</v>
+        <v>-0.7010999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.2334</v>
+        <v>-1.3102</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5323</v>
+        <v>0.6091</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3803</v>
+        <v>-0.4206</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.5838</v>
+        <v>-0.502</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2035</v>
+        <v>0.0814</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3208</v>
+        <v>-0.2805</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6496</v>
+        <v>-0.8082</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3288</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5441</v>
+        <v>1.158</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5441</v>
+        <v>1.158</v>
       </c>
       <c r="S8" t="n">
-        <v>1.8157</v>
+        <v>-0.6055</v>
       </c>
       <c r="T8" t="n">
-        <v>1.6882</v>
+        <v>-0.1768</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1275</v>
+        <v>-0.4287</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2702</v>
+        <v>-0.2859</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.0422</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.228</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. PEREZ ABELLEIRA</t>
+          <t>C. DIALLO TOURE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2217</v>
+        <v>-0.6149</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3579</v>
+        <v>-0.6574</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1362</v>
+        <v>0.0425</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7010999999999999</v>
+        <v>-1.7011</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3102</v>
+        <v>-3.2334</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6091</v>
+        <v>1.5323</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4206</v>
+        <v>-1.3803</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.502</v>
+        <v>-1.5838</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0814</v>
+        <v>0.2035</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2805</v>
+        <v>-0.3208</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8082</v>
+        <v>-1.6496</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5276999999999999</v>
+        <v>1.3288</v>
       </c>
       <c r="P9" t="n">
-        <v>1.158</v>
+        <v>1.5441</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.158</v>
+        <v>1.5441</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3927</v>
+        <v>0.8124</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9373</v>
+        <v>0.7651</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4554</v>
+        <v>0.0472</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2859</v>
+        <v>-1.2702</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.0422</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2859</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0626</v>
+        <v>-3.195</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3597</v>
+        <v>-0.5992</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7028</v>
+        <v>-2.5958</v>
       </c>
       <c r="G10" t="n">
         <v>-2.475</v>
@@ -1234,13 +1234,13 @@
         <v>0.386</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7456</v>
+        <v>0.122</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5803</v>
+        <v>0.1801</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1653</v>
+        <v>-0.0582</v>
       </c>
       <c r="V10" t="n">
         <v>-1.228</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0739</v>
+        <v>-3.4463</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.6527</v>
+        <v>-4.5337</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5788</v>
+        <v>1.0874</v>
       </c>
       <c r="G11" t="n">
         <v>-3.255</v>
@@ -1312,13 +1312,13 @@
         <v>2.3161</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1976</v>
+        <v>0.43</v>
       </c>
       <c r="T11" t="n">
-        <v>0.665</v>
+        <v>0.784</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8626</v>
+        <v>-0.354</v>
       </c>
       <c r="V11" t="n">
         <v>-0.0422</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.1232</v>
+        <v>13.0157</v>
       </c>
       <c r="E12" t="n">
-        <v>6.595399999999999</v>
+        <v>7.487900000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>5.5278</v>
+        <v>5.5277</v>
       </c>
       <c r="G12" t="n">
         <v>8.8047</v>
@@ -1366,7 +1366,7 @@
         <v>10.3741</v>
       </c>
       <c r="K12" t="n">
-        <v>2.740900000000001</v>
+        <v>2.7409</v>
       </c>
       <c r="L12" t="n">
         <v>7.633000000000001</v>
@@ -1390,13 +1390,13 @@
         <v>14.4756</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4078</v>
+        <v>2.3003</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8311</v>
+        <v>2.7234</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4233</v>
+        <v>-0.4234</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9843999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.121</v>
+        <v>11.1445</v>
       </c>
       <c r="E13" t="n">
-        <v>11.379</v>
+        <v>10.7782</v>
       </c>
       <c r="F13" t="n">
-        <v>0.742</v>
+        <v>0.3663</v>
       </c>
       <c r="G13" t="n">
         <v>8.929600000000001</v>
@@ -1468,13 +1468,13 @@
         <v>1.7371</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5196</v>
+        <v>0.543</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8871</v>
+        <v>0.2862</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6325</v>
+        <v>0.2567</v>
       </c>
       <c r="V13" t="n">
         <v>0.8999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. SANCHEZ MARROYO</t>
+          <t>J. GOMEZ MERODIO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,28 +1501,28 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.358</v>
+        <v>1.2003</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2116</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1464</v>
+        <v>0.4881</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0112</v>
+        <v>0.6098</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3125</v>
+        <v>0.3084</v>
       </c>
       <c r="I14" t="n">
         <v>0.3013</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1715</v>
+        <v>0.4495</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2122</v>
+        <v>0.4088</v>
       </c>
       <c r="L14" t="n">
         <v>0.0407</v>
@@ -1546,19 +1546,19 @@
         <v>0.579</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5043</v>
+        <v>0.0116</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0973</v>
+        <v>0.2628</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5929</v>
+        <v>-0.2512</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. MAESTRO STEELE</t>
+          <t>J. SANCHEZ MARROYO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8596</v>
+        <v>1.1247</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1018</v>
+        <v>0.7109</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2422</v>
+        <v>0.4138</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.1715</v>
+        <v>-0.0112</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8081</v>
+        <v>-0.3125</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.9796</v>
+        <v>0.3013</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6298</v>
+        <v>-0.1715</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0956</v>
+        <v>-0.2122</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.4659</v>
+        <v>0.0407</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.8013</v>
+        <v>0.1603</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2875</v>
+        <v>-0.1003</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.5137</v>
+        <v>0.2606</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0238</v>
+        <v>0.271</v>
       </c>
       <c r="T15" t="n">
-        <v>0.472</v>
+        <v>0.5966</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4482</v>
+        <v>-0.3255</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6562</v>
+        <v>0.2859</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. GOMEZ MERODIO</t>
+          <t>L. MAESTRO STEELE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5661</v>
+        <v>0.8728</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2115</v>
+        <v>0.9015</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3546</v>
+        <v>-0.0287</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6098</v>
+        <v>-1.1715</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3084</v>
+        <v>1.8081</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3013</v>
+        <v>-2.9796</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4495</v>
+        <v>0.6298</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4088</v>
+        <v>2.0956</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0407</v>
+        <v>-1.4659</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1603</v>
+        <v>-1.8013</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1003</v>
+        <v>-0.2875</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2606</v>
+        <v>-1.5137</v>
       </c>
       <c r="P16" t="n">
-        <v>0.579</v>
+        <v>1.3511</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.579</v>
+        <v>1.3511</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6227</v>
+        <v>0.037</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.238</v>
+        <v>0.2717</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3847</v>
+        <v>-0.2347</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6802</v>
+        <v>0.5089</v>
       </c>
       <c r="E17" t="n">
-        <v>0.473</v>
+        <v>1.0739</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1533</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>3.999</v>
@@ -1780,13 +1780,13 @@
         <v>0.965</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.433</v>
+        <v>-0.2439</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5208</v>
+        <v>0.08</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9122</v>
+        <v>-0.3239</v>
       </c>
       <c r="V17" t="n">
         <v>0.614</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3145</v>
+        <v>-1.3069</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3568</v>
+        <v>-0.8576</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9577</v>
+        <v>-0.4494</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8796</v>
@@ -1858,13 +1858,13 @@
         <v>0.965</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5301</v>
+        <v>0.5377</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7245</v>
+        <v>0.2238</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1943</v>
+        <v>0.3139</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6247</v>
+        <v>-2.3573</v>
       </c>
       <c r="E19" t="n">
         <v>-1.5104</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1143</v>
+        <v>-0.8469</v>
       </c>
       <c r="G19" t="n">
         <v>-3.2031</v>
@@ -1936,13 +1936,13 @@
         <v>1.5441</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0007</v>
+        <v>0.2667</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0172</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0165</v>
+        <v>0.2839</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.2919</v>
+        <v>-4.7241</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2565</v>
+        <v>-0.9560999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.0354</v>
+        <v>-3.768</v>
       </c>
       <c r="G20" t="n">
         <v>-2.2418</v>
@@ -2014,13 +2014,13 @@
         <v>1.3511</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9802</v>
+        <v>-0.4125</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6993</v>
+        <v>-0.3989</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2809</v>
+        <v>-0.0136</v>
       </c>
       <c r="V20" t="n">
         <v>-2.4559</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.6493</v>
+        <v>-7.4695</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.9352</v>
+        <v>-7.835</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2859</v>
+        <v>0.3655</v>
       </c>
       <c r="G21" t="n">
         <v>-7.1286</v>
@@ -2092,13 +2092,13 @@
         <v>1.7371</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.347</v>
+        <v>-0.1672</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5525</v>
+        <v>-0.4524</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2055</v>
+        <v>0.2852</v>
       </c>
       <c r="V21" t="n">
         <v>0.9843</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.467499999999999</v>
+        <v>-9.113799999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.845700000000001</v>
+        <v>-8.545199999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6218</v>
+        <v>-0.5686</v>
       </c>
       <c r="G22" t="n">
         <v>-7.7072</v>
@@ -2170,13 +2170,13 @@
         <v>0.772</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6022</v>
+        <v>-0.2485</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7297</v>
+        <v>-0.4293</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1275</v>
+        <v>0.1807</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-12.1234</v>
+        <v>-10.1204</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.527700000000001</v>
+        <v>-5.527600000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.595800000000001</v>
+        <v>-4.592899999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-8.804600000000001</v>
@@ -2224,7 +2224,7 @@
         <v>1.569500000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>8.149000000000001</v>
+        <v>8.148999999999999</v>
       </c>
       <c r="L23" t="n">
         <v>-6.5796</v>
@@ -2248,13 +2248,13 @@
         <v>11.5805</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.407999999999999</v>
+        <v>0.5949</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4234</v>
+        <v>0.4233000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.8312</v>
+        <v>0.1715</v>
       </c>
       <c r="V23" t="n">
         <v>0.9843999999999997</v>
